--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Dialog/Drama/kettle.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Dialog/Drama/kettle.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1012" uniqueCount="653">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="736">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -2447,25 +2447,8 @@
 Black and murky... just looking into it feels like it might swallow me whole.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">이게 「웅덩이」 인가.
-어둡고 탁해서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">… 쳐다보고만 있어도 삼켜질 것만 같군.</t>
-    </r>
+    <t xml:space="preserve">이게 「웅덩이」 인가.
+어둡고 탁해서… 쳐다보고만 있어도 삼켜질 것만 같군.</t>
   </si>
   <si>
     <t xml:space="preserve">気味の悪い場所です。イスシズルの用事を済ませて、早々に立ち去りましょう。</t>
@@ -2483,6 +2466,209 @@
   <si>
     <t xml:space="preserve">I cannot agree more.
 Just dripping a single drop into this "Pool". A simple task.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">그 의견에는 대찬성이야.
+이 「웅덩이」에 물방울 하나를 떨어뜨린다… 간단한 일이지.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">water_choice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">では、#pc、どちらの瓶を使う？ イスシズルに渡されたこの得体の知れない瓶か、ファリスさん特製の洗…聖水か。
+（…おい、#pc、聞こえるか？）
+（ファリスさんもついて来てしまったが、安心しろ。お前がどちらを選んでも、ばれないように上手くやってやる。お前の決断を尊重するよ）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">So, #pc, which bottle will you use? This eerie one Issizzle gave us, or Lady Farris’s... holy water?
+(...#pc, you hear me?)
+(Lady Farris ended up coming along, but don’t worry. Whichever one you choose, I’ll make sure she never finds out. I’ll respect your decision.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">그럼 이제, #pc. 어느 병을 쓸 거냐? 이스시즐이 넘긴 이 정체를 알 수 없는 병이냐, 아니면 패리스 양 특제 세… 성수냐.
+(…야, #pc, 들리냐?)
+(패리스 양도 따라오게 됐지만, 안심해라. 네가 어느 쪽을 고르든 안 걸리게 잘 해 줄게. 네 결단을 존중하니까.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">water1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">イスシズルの瓶を使う</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use Issizzle’s bottle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이스시즐의 병을 쓴다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">water2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ファリスの瓶を使う</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use Farris’s bottle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">패리스의 병을 쓴다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…イスシズルの瓶で間違いないか？
+とても穢れた匂いだ。この一滴は、やがて邪悪なるものを育むことだろう。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...This Issizzle’s bottle, yes?
+It reeks of corruption. This single drop will no doubt nurture something wicked.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+…이스시즐의 병, 확실하지?
+정말 더러운 냄새구만. 이 한 방울은, 마침내 사악한 무언가를 키워내게 될 테지.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">water_choice3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">はい</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">그래</t>
+  </si>
+  <si>
+    <t xml:space="preserve">いいえ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">아니</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…ファリスさんのこの瓶で間違いないか？
+とても…いい匂いだ。この一滴が何をもたらすのか、検討もつかないよ。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...This Lady Farris’s bottle, yes?
+It smells... wonderful. I can’t even guess what this one drop will bring.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…패리스 양의 병, 확실하지?
+정말… 좋은 냄새구만. 이 한 방울이 뭘 일으키게 될지, 감도 안 잡혀.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">water_choice2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">setFlag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">farris_water,1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">よし。では、私がこの瓶の雫を一滴、「淀み」に垂らしてこよう。
+いや、#pc、これぐらいはさせてくれ。お前だけに重荷を背負わすわけにはいかないさ。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All right. I’ll go drip a single drop from this bottle into the "Pool".
+No, #pc, let me do at least this much. I can’t let you bear all the burdens alone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">좋아. 그럼, 내가 내용물을 한 방울, 「웅덩이」에 떨구지.
+아니, #pc, 이 정도는 하게 해 주라. 너한테만 무거운 짐을 지게 할 수는 없으니까.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…この一滴で世界の命運が変わるかもしれない、そう思うと息が詰まるようだ。
+それにこの床がまた…妙にヌメヌメしていて…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...Thinking that a single drop might change the fate of the world... it’s almost suffocating.
+And this floor, it’s really slimy and...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…이 한 방울이 세상의 운명을 바꾸게 될지도 모른다, 그렇게 생각하니 숨이 막힐 지경이군.
+게다가 이 바닥도… 묘하게 미끌거려서…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sound</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">あ゛っ゛！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agh!!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">으악!!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">potion_sorin,-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">potion_farris,-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">お、落ち着け、私なら大丈夫だ！
+…ふぅ、全身びしょ濡れになってしまって気持ち悪いが、この「淀み」がそんなに深くなくて助かった。
+ハッ…瓶は…2本ともどこにいった？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C-Calm down, I’m fine!
+...Whew. I’m soaked from head to toe. It feels awful, but at least the "Pool" wasn’t that deep.
+Wait... where did both bottles go?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">지, 진정해! 나는 괜찮다!
+…후, 온몸이 다 젖어서 기분 나쁘지만, 이 「웅덩이」가 생각만큼 깊지가 않아서 살았네.
+핫… 병이… 두 개 다 어디 간 거지?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…ロイテル様…！！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...Lord Loytel...!!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…로이텔님…!!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ファリスさん、落ち着いて…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lady Farris, calm down...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">패리스 양, 진정해…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">後ろ、後ろです！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Behind — behind you!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">뒤, 뒤쪽 보세요!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">invoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">event_az</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bossText</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">az</t>
   </si>
   <si>
     <r>
@@ -2493,8 +2679,711 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t xml:space="preserve">그 의견에는 대찬성이야.
-이 </t>
+      <t xml:space="preserve">…ル</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">ヴァ・シェ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">ヌル・アザ゛ルゥ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">ル……ネ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">イフ・ダロゥン……サ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">ラ・クン</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">アグラ… 
+…ル</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">ヴァ・シェ……ル゛ェ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">ノル・シャ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">ラグン……ハ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">ザ… ！！</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">...RU=VA SHE=NUR AZZALUU=RU... NE=IF DALOON... SA=RA KUN=AGRA...
+...RU=VA SHE... L’E=NOR SHA=RAGUN... HA=ZA...!!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…루=바・셰=누르・아자루=루…… 네=이프・다론…… 사=라・쿤=아구라…
+…루=바・셰…… 루에=노르・샤=라군…… 하=자…!!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">な…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wh—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">뭐…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">何を言っているか全くわからないが、相当怒っているようだ。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I have no idea what it’s saying, but it sounds furious.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">뭔 소릴 하는지는 전혀 모르겠지만, 화가 많이 났구만.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">…ル</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">ヴァ・ザ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">ノゥ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">ル゛ェ……アグ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">シェ…アグシェネ゛…イ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">ドラ……シャ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">ラ・フン…… ！！</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">...RU=VA ZA=NOO=LE... AG=SHE... AGSHENE... I=DRA... SHA=LA FUN...!!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…루=바・자=노우=루에…… 아구=셰… 아구셰네… 이=도라…… 샤=라・훈……!!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">おお…不浄なる者アズラシズル…かつて地上を恐怖に陥れ、神々に封印されし邪神です…！</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">The Unpure, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">Azrasizzle</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">... the ancient evil god once sealed by the gods themselves...!</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">오오… 부정한 자 아즈라시즐… 일찍이 지상을 공포에 빠뜨리고, 신들에게 봉인당한 사악한 신입니다…!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…これが「淀み」の正体、いずれ芽吹く災いの種か。ちょうどいい、そんなものは、今ここで刈り取ってやる。
+ふっ、流石の邪神も、そのフレッシュな香りでは思う存分に力を発揮できまい。
+さあ、#pc、後は任せたぞ！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...So this is the true nature of the "Pool". A seed of calamity waiting to sprout. It should end here and now.
+Heh... even an evil god probably can’t unleash its full strength with such a fresh scent clinging to it.
+Go on, #pc. I leave the rest to you!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…이게  「웅덩이」의 정체, 언젠가 자라날 재앙의 씨앗인가. 마침 잘 됐어, 지금 이 자리에서 싹을 잘라내 주마.
+훗, 사악한 신이든 뭐든, 그렇게나 상쾌한 향을 풍기면서 제 힘을 발휘할 수는 없겠지.
+자아, #pc! 뒤는 맡긴다!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">event_az2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">event_az3</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">quest_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">into_darkness6</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">alphaIn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">おお、やったな、#pc！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Well done, #pc!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">오오, 해냈구만, #pc!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">お見事です、#player様。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Splendid work, #player.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">훌륭합니다, #player님.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">この化け物が出てきた時は、もうダメかと思ったが…まあ、 終わってみればなんとかなるものだ。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When that monster showed up, I thought we were finished... but in the end, things have a way of working out.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이 괴물이 튀어나왔을 땐 다 틀렸다 싶었는데… 뭐, 끝나고 보니 어떻게든 되는 법이구만.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">イスシズルめ…とんでもない奴だ。遠い未来とはいえ、自らの野望のためにこんなものを世に解き放とうと考えていたとは。
+しかし、困ったことになったな。これでは奴との約束が果たせないぞ。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Issizzle... that wretch. Even if the calamity lies far in the future, I can’t believe he’d unleash something like this for the sake of his ambition.
+But this is troubling. Now we can’t keep our promise to him.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이스시즐 이 자식… 뭐 그딴 놈이 다 있담. 아무리 먼 미래라 해도, 자기 야망 때문에 이런 걸 세상에 풀어놓을 생각을 하다니.
+하지만, 곤란해졌군. 이걸로 놈이랑 한 약속을 지킬 수가 없게 됐으니 말이야.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">私たちは何も見なかったし、ここでは何も起きなかった…いいですね、ロイテル様？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We saw nothing, and nothing happened here... Isn’t that right, Lord Loytel?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저희는 아무 것도 못 봤고, 여기서는 아무 일도 없었습니다… 아시겠죠, 로이텔님?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…ああ。奴が簡単に信じるとは思い難いが、そう話すしかないだろう。
+よし、ひとまずは拠点に帰って、イスシズルを待つとしよう。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...Yes. I doubt he’ll believe it so easily, but that’s all we can say.
+All right. Let’s return to the base and wait for Issizzle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…그래. 놈이 순순히 믿어줄 것 같진 않지만, 그렇게 얘기할 수밖에 없겠지.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">quest_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">into_darkness7</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">bg_road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ケトル…ちょっといい？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kettle... can I talk to you?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">케틀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">… 잠깐 괜찮아?</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">どうしたんだい、クルイツゥア？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, Quruitzia?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">왜 그러니, 쿠루이차?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">さっきね、見たことのない黒ローブの男の子が、私とコルゴンをじっと見ていたの。だから、話しかけようとしたら、デミタスがすごい剣幕で割って入って来て、その子と口論を始めて…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earlier... I saw a boy in a black robe I’d never seen before, just staring at me and Corgon. So I tried to talk to him, but Demitas barged in all furious and started arguing with him...</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">아까 전에, 검은 로브 차림을 한 본 적 없는 남자애가, 나랑 코르곤을 쭉 쳐다봤어. 말을 걸어보려 하니까, 데미타스가 엄청 화내면서 끼어들어서, 그 애랑 말싸움을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">…</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">…そうか、そろそろ現れる頃だと思っていたよ。
+その黒ローブの子はソリン、イスシズルの人間の姿だ。デミタスと彼とは、過去にちょっとした因縁があってね。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I see... I thought he’d be showing up about now.
+The boy in black is Sorin—Issizzle’s human form. Demitas and he have... a bit of history.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…그런가. 슬슬 올 때가 됐다고 생각했지.
+그 검은 로브를 입은 아이는 소린, 이스시즐의 인간 모습이야. 데미타스랑 소린은 예전에 인연이 조금 있어서 말이야.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">あの子が…イスシズル？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">That boy... is Issizzle?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">그 애가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">… 이스시즐?</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">恐れることは何もない、クルイツゥア。私たちは死者の洞窟で彼との約束を果たしたんだから。
+そうだね、ロイテル？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There’s nothing to fear, Quruitzia. We kept our promise to him in the Crypt of the Damned.
+Isn’t that right, Loytel?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">무서워할 것 없어, 쿠루이차. 우린 죽은 자의 동굴에서 약속을 확실히 지켰으니 말이야.
+그렇지, 로이텔?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…その、ケトル…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...Well, Kettle...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…그, 케틀…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">何かな？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">응?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">い、いや、確かにもう危険は去ったはずだが…念のために聞かせてくれ。イスシズルを怒らせると、一体どうなるんだ？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-nothing... I’m sure the danger has passed, but just in case, what happens if we make Issizzle angry?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">아, 아니, 확실히 이제 위험할 것은 없지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">… 혹시 모르니 묻지. 이스시즐을 화나게 만들면, 대체 어떻게 되는 거지?</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">その気になれば、国ひとつ簡単に滅ぼす力を持った魔術師だ。彼は、この時代で私たちが最も怒らせたくない相手の一人だろうね。
+でも、心配には及ばないさ、ロイテル。なぜなら、ふふ、もし君が「彼を怒らせることでもしていた」のなら、君はとっくに地面の下で眠っているだろうからね。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He is a sorcerer powerful enough to wipe out an entire kingdom. In this age, he is certainly one of the last people we want to provoke.
+But don’t worry, Loytel. Because &lt;b&gt;if you’d done anything to anger him&lt;/b&gt;, you’d already be sleeping under the ground, hehe.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">마음만 먹으면 나라 하나 정도는 간단히 없앨 수 있는 힘을 가진 마술사야. 이 시대에서 가장 화나게 만들고 싶지 않은 상대 중 하나겠지.
+하지만 걱정할 건 없어, 로이텔. 왜냐하면, 후후, 만약 네가 </t>
     </r>
     <r>
       <rPr>
@@ -2504,21 +3393,23 @@
         <family val="0"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve">「웅덩이」에 물방울 하나를 떨어뜨린다… 간단한 일이지.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">water_choice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">では、#pc、どちらの瓶を使う？ イスシズルに渡されたこの得体の知れない瓶か、ファリスさん特製の洗…聖水か。
-（…おい、#pc、聞こえるか？）
-（ファリスさんもついて来てしまったが、安心しろ。お前がどちらを選んでも、ばれないように上手くやってやる。お前の決断を尊重するよ）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">So, #pc, which bottle will you use? This eerie one Issizzle gave us, or Lady Farris’s... holy water?
-(...#pc, you hear me?)
-(Lady Farris ended up coming along, but don’t worry. Whichever one you choose, I’ll make sure she never finds out. I’ll respect your decision.)</t>
+      <t xml:space="preserve">「그가 화낼 짓이라도 했다」면, 넌 한참 전에 땅 속에서 잠을 자고 있었을 테니까 말이야.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">…は…ははは、そうか…！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...H-hahaha... I see...!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…하…하하하, 그렇구만…!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（ひそひそ）ファリスさん、「淀み」で起こったことは、絶対に奴には黙っていよう。ケトルにだって、もうだいぶ怪しまれているぞ。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(whisper) Lady Farris—whatever happened in the "Pool", we must absolutely keep it from him. Even Kettle is already growing suspicious.</t>
   </si>
   <si>
     <r>
@@ -2529,7 +3420,7 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t xml:space="preserve">그럼 이제, #pc. 어느 병을 쓸 거냐? 이스시즐이 넘긴 이 정체를 알 수 없는 병이냐, 아니면 패리스 양 특제 세</t>
+      <t xml:space="preserve">(소근소근) 패리스 양, </t>
     </r>
     <r>
       <rPr>
@@ -2539,97 +3430,14 @@
         <family val="0"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve">… 성수냐.
-(…야, #pc, 들리냐?)
-(패리스 양도 따라오게 됐지만, 안심해라. 네가 어느 쪽을 고르든 안 걸리게 잘 해 줄게. 네 결단을 존중하니까.)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">water1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">イスシズルの瓶を使う</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Use Issizzle’s bottle.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">이스시즐의 병을 쓴다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">water2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ファリスの瓶を使う</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Use Farris’s bottle.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">패리스의 병을 쓴다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…イスシズルの瓶で間違いないか？
-とても穢れた匂いだ。この一滴は、やがて邪悪なるものを育むことだろう。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">...This Issizzle’s bottle, yes?
-It reeks of corruption. This single drop will no doubt nurture something wicked.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-…이스시즐의 병, 확실하지?
-정말 더러운 냄새구만. 이 한 방울은, 마침내 사악한 무언가를 키워내게 될 테지.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">water_choice3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">はい</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">그래</t>
-  </si>
-  <si>
-    <t xml:space="preserve">いいえ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">아니</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…ファリスさんのこの瓶で間違いないか？
-とても…いい匂いだ。この一滴が何をもたらすのか、検討もつかないよ。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">...This Lady Farris’s bottle, yes?
-It smells... wonderful. I can’t even guess what this one drop will bring.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…패리스 양의 병, 확실하지?
-정말… 좋은 냄새구만. 이 한 방울이 뭘 일으키게 될지, 감도 안 잡혀.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">water_choice2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">setFlag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">farris_water,1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">よし。では、私がこの瓶の雫を一滴、「淀み」に垂らしてこよう。
-いや、#pc、これぐらいはさせてくれ。お前だけに重荷を背負わすわけにはいかないさ。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All right. I’ll go drip a single drop from this bottle into the "Pool".
-No, #pc, let me do at least this much. I can’t let you bear all the burdens alone.</t>
+      <t xml:space="preserve">「웅덩이」에서 일어났던 일은 그 녀석에게는 반드시 숨기자. 케틀한테도 이미 상당히 의심을 받고 있다고.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">（ひそひそ）はい、ロイテル様…唄にできないのは心残りですが、今回ばかりは止むを得ません。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(whisper) Yes, Lord Loytel... It’s a shame we can’t turn it into a song, but it can’t be helped this time.</t>
   </si>
   <si>
     <r>
@@ -2640,7 +3448,7 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t xml:space="preserve">좋아. 그럼, 내가 내용물을 한 방울, </t>
+      <t xml:space="preserve">(소근소근) 네, 로이텔님</t>
     </r>
     <r>
       <rPr>
@@ -2650,52 +3458,35 @@
         <family val="0"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve">「웅덩이」에 떨구지.
-아니, #pc, 이 정도는 하게 해 주라. 너한테만 무거운 짐을 지게 할 수는 없으니까.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">…この一滴で世界の命運が変わるかもしれない、そう思うと息が詰まるようだ。
-それにこの床がまた…妙にヌメヌメしていて…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">...Thinking that a single drop might change the fate of the world... it’s almost suffocating.
-And this floor, it’s really slimy and...</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…이 한 방울이 세상의 운명을 바꾸게 될지도 모른다, 그렇게 생각하니 숨이 막힐 지경이군.
-게다가 이 바닥도… 묘하게 미끌거려서…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sound</t>
-  </si>
-  <si>
-    <t xml:space="preserve">slip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">あ゛っ゛！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agh!!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">으악!!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">potion_sorin,-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">potion_farris,-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">お、落ち着け、私なら大丈夫だ！
-…ふぅ、全身びしょ濡れになってしまって気持ち悪いが、この「淀み」がそんなに深くなくて助かった。
-ハッ…瓶は…2本ともどこにいった？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C-Calm down, I’m fine!
-...Whew. I’m soaked from head to toe. It feels awful, but at least the "Pool" wasn’t that deep.
-Wait... where did both bottles go?</t>
+      <t xml:space="preserve">… 노래로 지을 수 없다는 것이 아쉽지만, 이번만큼은 어쩔 수가 없네요.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">…さて、デミタスもそろそろ鎮まっている頃だろう。私たちも話を聞きに行こう。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...All right. Demitas has probably cooled off by now. Let’s go hear what he has to say.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…그럼 이제, 데미타스도 슬슬 진정됐겠지. 우리도 이야기나 들으러 가 보자.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…では、約束は無事果たされたと考えて良いのですね？
+なに、ただの確認ですよ。「淀み」への干渉は、僕にもすぐ感じ取ることができました。ただ…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...Then we may assume the promise was fulfilled without incident?
+No, it’s just a confirmation. I sensed the interference with the "Pool" at once. However...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…그렇다면, 약속은 무사히 지켜졌다고 생각해도 되겠지요?
+뭐, 그냥 확인한 겁니다. 「웅덩이」에 간섭한 것은 저도 이미 느꼈으니. 다만…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ただ…？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">However...?</t>
   </si>
   <si>
     <r>
@@ -2706,8 +3497,7 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t xml:space="preserve">지, 진정해! 나는 괜찮다!
-</t>
+      <t xml:space="preserve">다만</t>
     </r>
     <r>
       <rPr>
@@ -2717,24 +3507,18 @@
         <family val="0"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve">…후, 온몸이 다 젖어서 기분 나쁘지만, 이 「웅덩이」가 생각만큼 깊지가 않아서 살았네.
-핫… 병이… 두 개 다 어디 간 거지?</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">…ロイテル様…！！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">...Lord Loytel...!!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…로이텔님…!!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ファリスさん、落ち着いて…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lady Farris, calm down...</t>
+      <t xml:space="preserve">…?</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ただ、その時を境に、僕の魔力の一部が失われたのです。厳密に言えば、僕は「イスシズル」の不死の肉体を失ってしまった。
+フッ、もちろん、それはつまり、再び「淀み」が動き出したという喜ばしい確証でもあるのです。
+心配には及びませんよ。「淀み」でかの者の力が増せば、僕の魔力もまた戻って来るでしょう。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From that moment on, a portion of my magic was lost. To be precise, I lost Issizzle’s immortal body.
+Heh, but that is, in itself, a most welcome proof that the "Pool" has begun to stir again.
+There is no need for concern. As that being’s power grows within the "Pool", my own magic will return as well.</t>
   </si>
   <si>
     <r>
@@ -2745,7 +3529,7 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t xml:space="preserve">패리스 양, 진정해</t>
+      <t xml:space="preserve">다만, 그 때를 기점으로, 제 마력의 일부가 사라졌습니다. 엄밀히 말하자면 저는 </t>
     </r>
     <r>
       <rPr>
@@ -2755,32 +3539,18 @@
         <family val="0"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve">…</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">後ろ、後ろです！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Behind — behind you!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">뒤, 뒤쪽 보세요!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">invoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">event_az</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bossText</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">az</t>
+      <t xml:space="preserve">「이스시즐」의 불사의 육신을 잃었지요.
+훗, 물론, 그것은 즉 「웅덩이」가 다시금 활동하기 시작했다는 기쁜 확증이기도 합니다.
+걱정할 필요는 없습니다. 「웅덩이」의 그자가 힘을 키우면, 제 마력도 다시 돌아올 테니 말입니다.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">魔力が失われただって？　それは良かっ…いや、災難だったな！
+では、もうコルゴンやクルイツゥアに身の危険はないということか。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You lost some of your power? That’s wonderf— no, that’s terrible!
+Then does that mean Corgon and Quruitzia are no longer in danger?</t>
   </si>
   <si>
     <r>
@@ -2791,18 +3561,104 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t xml:space="preserve">…ル</t>
-    </r>
+      <t xml:space="preserve">마력을 잃었다고? 그건 다행</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">… 아니, 끔찍하군!
+그럼, 이제 코르곤이랑 쿠루이차가 위험하지는 않다는 건가.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">…師よ、ここにいる愚か者にも理解できるよう、後でよく教えてやるといいでしょう。魔術師にとって言葉がどれほど重いものかを。
+僕は約束を守ると決めています。たとえ今すぐにでも、その男が気に触ったという理由だけで、この場を惨状に変えられる魔力が僕に残っているとしても、です。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…Master, you would do well to explain this properly later, so that even the fool standing here may understand how heavy words are to a mage. 
+I have decided to keep my promise, even if I still possess the magic to turn this place into a scene of devastation at this very moment, for no reason other than that fool displeasing me.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…스승이시여, 여기 모인 이 어리석은 자들도 이해할 수 있도록, 나중에 잘 설명해 주십시오. 마술사에게 말이라는 것이 얼마나 무거운지를.
+저는 약속을 지키기로 했습니다. 저 남자가 심기를 거슬렀다는 이유 하나로, 지금 당장이라도 이곳을 끔찍한 참상으로 바꿔버릴 수 있는 마력이 남아있는데도, 말입니다.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="0"/>
         <charset val="128"/>
       </rPr>
-      <t xml:space="preserve">=</t>
-    </r>
+      <t xml:space="preserve">…フッ、まあ構いません。どのみち、この場に居る者の大半とは、もう二度と顔を合わせることもないのです。
+竜の子と魔女という珍しいものが見れた上に、古き友とも実に和やかな交流ができたのですから、わざわざ足を運んだだけの甲斐はあったというものです。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">では、師よ。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">...No matter. In any case, I doubt I shall ever meet most of those present here again.
+To have seen such curiosities as a dragon child and a witch, and to share so cordial an exchange with an old friend, I suppose it was worth the trouble of coming.
+Now then, Master.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…훗, 뭐, 됐습니다. 어찌 됐든 이곳에 사는 자들 중 대다수와는 이제 두 번 다시 마주할 일이 없을 테니.
+용의 아이와 마녀라는 보기 드문 것을 본 데다, 오랜 벗과도 실로 화목하게 교류를 할 수 있었으니 굳이 발걸음을 옮긴 보람은 있었다고 해야겠지요.
+그럼 이제, 스승이시여.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…ソリン、その身体であの古城に帰る気かい？
+悪気はないけど、この前訪れた時は、とても「人間」がくつろげる場所だとは思えなかったよ。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...Sorin, are you really going back to that old castle in your...current body?
+No offense, but last time I visited your castle, it hardly felt like a place a "human" could relax.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…소린, 그 몸으로 그 고성으로 돌아갈 거니?
+기분 나쁘다면 미안하지만, 저번에 찾아갔을 땐 그 성은 도저히 「인간」이 편히 쉴 수 있는 곳 같지 않았어.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ふふ、そんなに怖い顔をしないでくれ。言い直すよ。
+君の魔力が戻るまで、ここで暮らしてみないか、ソリン？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hehe, don’t make such a frightening face. Let me put it another way.
+Why not live here with us until your magic returns, Sorin? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">후후, 그렇게 무서운 표정 짓지 말렴. 다르게 말해 볼게.
+네 마력이 돌아올 때까지, 이곳에서 살아보지 않겠니, 소린?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（スーッ）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Takes a deep breath) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">（쓰읍）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">それは…意外な申し出です、師よ。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">That is... an unexpected offer, Master.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -2811,18 +3667,88 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t xml:space="preserve">ヴァ・シェ</t>
+      <t xml:space="preserve">그것은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">… 의외의 제안이시군요, 스승님.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">…そして、僕にとって好都合とも言えるでしょう。
+</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="0"/>
         <charset val="128"/>
       </rPr>
-      <t xml:space="preserve">=</t>
-    </r>
+      <t xml:space="preserve">竜の子と魔女の邂逅が意味するもの、 運命の糸に引かれた冒険者、そして何よりも師よ、魔石の秘密を知ってから、あなたという存在そのものが、僕の好奇心を離さないのです。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">...And one that is quite convenient for me.
+The meaning behind the meeting of the dragon child and the witch, the adventurer drawn by the threads of fate, and above all, Master—ever since I learned the secret of the magic stone, your very existence has refused to let go of my curiosity.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…그리고, 꽤나 구미가 당긴다고도 말할 수 있겠습니다.
+용의 아이와 마녀와의 해후가 의미하는 것, 운명의 실에 이끌린 모험가, 그리고 무엇보다 스승이시여, 마석의 비밀을 알게 되었을 때부터 당신이라는 존재 자체가 제 호기심을 자극하고 있습니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">もちろん、ただで宿を得るつもりはありません。
+僕がここに留まる見返りとして、何をお望みですか？ 失われし上古の魔法書、不老不死の薬、あるいは、休むことなく働き続ける死者の軍団でも作ってみせましょうか？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Of course, I have no intention of taking lodging for free.
+What would you desire in return? A lost grimoire of the ancient age, an elixir of immortality, or perhaps an army of the dead that never tires of labor?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">물론, 그냥 묵을 생각은 없습니다.
+제가 이곳에 머무는 대가로, 무엇을 바라십니까? 잊힌 고대의 마도서, 불로불사의 약, 아니면 쉬지 않고 일하는 시체 군단이라도 만들어 드릴까요?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">見返りか、そうだね、コルゴンがボロボロにした鍋の修理ぐらいは頼ませてもらうとするよ。
+だけど、まずは君の滞在を歓迎しよう。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">そしてソリン、まだ私を師と呼ぶのなら、覚えておくといい。君も…私も、この世界にはまだ多くの学ぶべきことが残っているんだ、どれだけ長生きだろうともね。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Well, I suppose I’ll at least ask you to repair the pots Corgon battered to pieces.
+But regardless, I welcome your stay here. 
+And Sorin, if you still call me your Master, remember. We still have much to learn from this world, however long our lives may be. </t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -2831,745 +3757,19 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t xml:space="preserve">ヌル・アザ゛ルゥ</t>
+      <t xml:space="preserve">대가라. 그럼, 코르곤이 너덜너덜하게 만든 냄비를 고치는 것 정도는 맡길게.
+하지만 우선은, 네가 이곳에 머무는 것을 환영하지.
+그리고 소린, 여전히 나를 스승이라고 부를 거라면, 잘 알아둬. 너도</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">ル……ネ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">イフ・ダロゥン……サ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">ラ・クン</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">アグラ… 
-…ル</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">ヴァ・シェ……ル゛ェ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">ノル・シャ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">ラグン……ハ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">ザ… ！！</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">...RU=VA SHE=NUR AZZALUU=RU... NE=IF DALOON... SA=RA KUN=AGRA...
-...RU=VA SHE... L’E=NOR SHA=RAGUN... HA=ZA...!!</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="0"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve">…루=바</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">・셰=누르・아자루=루</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">…… 네=이프</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">・다론</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">…… 사=라</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">・쿤=아구라</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">…
-…루=바</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">・셰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">…… 루에=노르</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">・샤=라군</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">…… 하=자…!!</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">な…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wh—</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">뭐</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">…</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">何を言っているか全くわからないが、相当怒っているようだ。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I have no idea what it’s saying, but it sounds furious.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">뭔 소릴 하는지는 전혀 모르겠지만, 화가 많이 났구만.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">…ル</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">ヴァ・ザ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">ノゥ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">ル゛ェ……アグ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">シェ…アグシェネ゛…イ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">ドラ……シャ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">ラ・フン…… ！！</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">...RU=VA ZA=NOO=LE... AG=SHE... AGSHENE... I=DRA... SHA=LA FUN...!!</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">…루=바</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">・자=노우=루에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">…… 아구=셰… 아구셰네… 이=도라…… 샤=라</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">・훈</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">……!!</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">おお…不浄なる者アズラシズル…かつて地上を恐怖に陥れ、神々に封印されし邪神です…！</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">The Unpure, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">Azrasizzle</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">... the ancient evil god once sealed by the gods themselves...!</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">오오</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">… 부정한 자 아즈라시즐… 일찍이 지상을 공포에 빠뜨리고, 신들에게 봉인당한 사악한 신입니다…!</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">…これが「淀み」の正体、いずれ芽吹く災いの種か。ちょうどいい、そんなものは、今ここで刈り取ってやる。
-ふっ、流石の邪神も、そのフレッシュな香りでは思う存分に力を発揮できまい。
-さあ、#pc、後は任せたぞ！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">...So this is the true nature of the "Pool". A seed of calamity waiting to sprout. It should end here and now.
-Heh... even an evil god probably can’t unleash its full strength with such a fresh scent clinging to it.
-Go on, #pc. I leave the rest to you!</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">…이게 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">「웅덩이」의 정체, 언젠가 자라날 재앙의 씨앗인가. 마침 잘 됐어, 지금 이 자리에서 싹을 잘라내 주마.
-훗, 사악한 신이든 뭐든, 그렇게나 상쾌한 향을 풍기면서 제 힘을 발휘할 수는 없겠지.
-자아, #pc! 뒤는 맡긴다!</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">event_az2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">event_az3</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">quest_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">into_darkness6</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">alphaIn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">おお、やったな、#pc！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Well done, #pc!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">오오, 해냈구만, #pc!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">お見事です、#player様。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Splendid work, #player.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">훌륭합니다, #player님.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">この化け物が出てきた時は、もうダメかと思ったが…まあ、 終わってみればなんとかなるものだ。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">When that monster showed up, I thought we were finished... but in the end, things have a way of working out.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">이 괴물이 튀어나왔을 땐 다 틀렸다 싶었는데</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">… 뭐, 끝나고 보니 어떻게든 되는 법이구만.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">イスシズルめ…とんでもない奴だ。遠い未来とはいえ、自らの野望のためにこんなものを世に解き放とうと考えていたとは。
-しかし、困ったことになったな。これでは奴との約束が果たせないぞ。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Issizzle... that wretch. Even if the calamity lies far in the future, I can’t believe he’d unleash something like this for the sake of his ambition.
-But this is troubling. Now we can’t keep our promise to him.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">이스시즐 이 자식</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">… 뭐 그딴 놈이 다 있담. 아무리 먼 미래라 해도, 자기 야망 때문에 이런 걸 세상에 풀어놓을 생각을 하다니.
-하지만, 곤란해졌군. 이걸로 놈이랑 한 약속을 지킬 수가 없게 됐으니 말이야.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">私たちは何も見なかったし、ここでは何も起きなかった…いいですね、ロイテル様？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">We saw nothing, and nothing happened here... Isn’t that right, Lord Loytel?</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">저희는 아무 것도 못 봤고, 여기서는 아무 일도 없었습니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">… 아시겠죠, 로이텔님?</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">…ああ。奴が簡単に信じるとは思い難いが、そう話すしかないだろう。
-よし、ひとまずは拠点に帰って、イスシズルを待つとしよう。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">...Yes. I doubt he’ll believe it so easily, but that’s all we can say.
-All right. Let’s return to the base and wait for Issizzle.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…그래. 놈이 순순히 믿어줄 것 같진 않지만, 그렇게 얘기할 수밖에 없겠지.</t>
+      <t xml:space="preserve">… 나도, 이 세계에는 아직 배워야 할 것들이 많이 남아 있어. 얼마나 오래 살 수 있든 간에 말이야.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -3580,7 +3780,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="21">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3674,9 +3874,22 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <color rgb="FF000000"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
       <charset val="129"/>
     </font>
     <font>
@@ -3688,22 +3901,21 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="0"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="0"/>
       <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="128"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="0"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="3">
@@ -3754,7 +3966,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3819,7 +4031,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3827,11 +4043,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4033,7 +4249,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:IX400"/>
+  <dimension ref="A1:IX451"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.85"/>
@@ -4043,9 +4259,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="7.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="60.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="53.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="45.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="60.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="52.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="53.39"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4089,7 +4305,7 @@
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I2" s="1" t="n">
         <f aca="false">MAX(I4:I1048576)</f>
-        <v>235</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4102,7 +4318,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I8" s="1" t="n">
         <v>1</v>
       </c>
@@ -4306,7 +4522,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I28" s="1" t="n">
         <v>23</v>
       </c>
@@ -4377,7 +4593,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I36" s="1" t="n">
         <v>12</v>
       </c>
@@ -4449,7 +4665,7 @@
       <c r="J40" s="4"/>
       <c r="K40" s="5"/>
     </row>
-    <row r="41" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I41" s="1" t="n">
         <v>16</v>
       </c>
@@ -4463,7 +4679,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="104.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I42" s="1" t="n">
         <v>17</v>
       </c>
@@ -4656,7 +4872,7 @@
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
     </row>
-    <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I59" s="1" t="n">
         <v>24</v>
       </c>
@@ -4704,7 +4920,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I62" s="1" t="n">
         <v>27</v>
       </c>
@@ -4852,7 +5068,7 @@
       <c r="J73" s="4"/>
       <c r="K73" s="5"/>
     </row>
-    <row r="74" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E74" s="5"/>
       <c r="F74" s="9"/>
       <c r="G74" s="5" t="s">
@@ -4910,7 +5126,7 @@
       <c r="J78" s="4"/>
       <c r="K78" s="5"/>
     </row>
-    <row r="79" customFormat="false" ht="104.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G79" s="1" t="s">
         <v>110</v>
       </c>
@@ -4941,7 +5157,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G81" s="1" t="s">
         <v>110</v>
       </c>
@@ -5352,7 +5568,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G114" s="5" t="s">
         <v>110</v>
       </c>
@@ -5369,7 +5585,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="98.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="109.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G115" s="5" t="s">
         <v>110</v>
       </c>
@@ -5564,7 +5780,7 @@
       <c r="J128" s="11"/>
       <c r="K128" s="5"/>
     </row>
-    <row r="129" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G129" s="5" t="s">
         <v>181</v>
       </c>
@@ -5751,7 +5967,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G140" s="5" t="s">
         <v>110</v>
       </c>
@@ -5799,7 +6015,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="143" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G143" s="5" t="s">
         <v>110</v>
       </c>
@@ -6657,7 +6873,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E175" s="5"/>
       <c r="F175" s="5"/>
       <c r="G175" s="5" t="s">
@@ -6733,7 +6949,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E179" s="5"/>
       <c r="F179" s="5"/>
       <c r="G179" s="5" t="s">
@@ -6771,7 +6987,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="181" customFormat="false" ht="104.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E181" s="5"/>
       <c r="F181" s="5"/>
       <c r="G181" s="5" t="s">
@@ -6790,7 +7006,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E182" s="5"/>
       <c r="F182" s="5"/>
       <c r="G182" s="5" t="s">
@@ -6809,7 +7025,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E183" s="5"/>
       <c r="F183" s="5"/>
       <c r="G183" s="5" t="s">
@@ -6828,7 +7044,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="184" customFormat="false" ht="127.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" customFormat="false" ht="104.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E184" s="5"/>
       <c r="F184" s="5"/>
       <c r="G184" s="5" t="s">
@@ -7441,7 +7657,7 @@
     <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="M197" s="1"/>
     </row>
-    <row r="198" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G198" s="5" t="s">
         <v>303</v>
       </c>
@@ -7458,7 +7674,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G199" s="5" t="s">
         <v>163</v>
       </c>
@@ -7475,7 +7691,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="200" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="104.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G200" s="5" t="s">
         <v>303</v>
       </c>
@@ -7509,7 +7725,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="202" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="202" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G202" s="5" t="s">
         <v>163</v>
       </c>
@@ -7526,7 +7742,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="203" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" customFormat="false" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G203" s="5" t="s">
         <v>303</v>
       </c>
@@ -7543,7 +7759,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="204" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" customFormat="false" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G204" s="5" t="s">
         <v>303</v>
       </c>
@@ -7645,7 +7861,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="210" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="210" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G210" s="5" t="s">
         <v>163</v>
       </c>
@@ -7747,7 +7963,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="216" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="216" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G216" s="5" t="s">
         <v>303</v>
       </c>
@@ -7855,7 +8071,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="224" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="224" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E224" s="5"/>
       <c r="F224" s="5"/>
       <c r="G224" s="5" t="s">
@@ -7893,7 +8109,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="226" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="226" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E226" s="5"/>
       <c r="F226" s="5"/>
       <c r="G226" s="5" t="s">
@@ -7912,7 +8128,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="227" customFormat="false" ht="127.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="227" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E227" s="5"/>
       <c r="F227" s="5"/>
       <c r="G227" s="5" t="s">
@@ -8544,7 +8760,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="242" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="242" customFormat="false" ht="104.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G242" s="5" t="s">
         <v>303</v>
       </c>
@@ -8561,7 +8777,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="243" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="243" customFormat="false" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G243" s="5" t="s">
         <v>303</v>
       </c>
@@ -8578,7 +8794,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="244" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="244" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G244" s="5" t="s">
         <v>163</v>
       </c>
@@ -8595,7 +8811,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="245" customFormat="false" ht="150.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="245" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G245" s="5" t="s">
         <v>163</v>
       </c>
@@ -8612,7 +8828,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="246" customFormat="false" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="246" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G246" s="5" t="s">
         <v>163</v>
       </c>
@@ -8646,7 +8862,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="248" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="248" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G248" s="5" t="s">
         <v>303</v>
       </c>
@@ -8680,7 +8896,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="250" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="250" customFormat="false" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G250" s="5" t="s">
         <v>303</v>
       </c>
@@ -8799,7 +9015,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="257" customFormat="false" ht="104.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="257" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G257" s="5" t="s">
         <v>303</v>
       </c>
@@ -8833,7 +9049,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="259" customFormat="false" ht="138.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="259" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G259" s="5" t="s">
         <v>303</v>
       </c>
@@ -8901,7 +9117,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="263" customFormat="false" ht="127.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="263" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G263" s="5" t="s">
         <v>303</v>
       </c>
@@ -9323,7 +9539,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="300" customFormat="false" ht="173.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="300" customFormat="false" ht="162" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G300" s="5" t="s">
         <v>181</v>
       </c>
@@ -9340,7 +9556,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="301" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="301" customFormat="false" ht="104.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G301" s="5" t="s">
         <v>57</v>
       </c>
@@ -9357,7 +9573,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="302" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="302" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G302" s="5" t="s">
         <v>57</v>
       </c>
@@ -9408,7 +9624,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="305" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="305" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G305" s="5" t="s">
         <v>57</v>
       </c>
@@ -9527,7 +9743,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="313" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="313" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G313" s="5" t="s">
         <v>57</v>
       </c>
@@ -9544,7 +9760,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="314" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="314" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G314" s="5" t="s">
         <v>181</v>
       </c>
@@ -9612,7 +9828,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="318" customFormat="false" ht="127.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="318" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G318" s="5" t="s">
         <v>57</v>
       </c>
@@ -9740,7 +9956,7 @@
       <c r="K335" s="5" t="s">
         <v>547</v>
       </c>
-      <c r="L335" s="4" t="s">
+      <c r="L335" s="2" t="s">
         <v>548</v>
       </c>
     </row>
@@ -9767,7 +9983,7 @@
       <c r="J337" s="4"/>
       <c r="K337" s="5"/>
     </row>
-    <row r="338" customFormat="false" ht="46.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="338" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F338" s="14"/>
       <c r="G338" s="1" t="s">
         <v>57</v>
@@ -9793,7 +10009,7 @@
       <c r="J339" s="4"/>
       <c r="K339" s="5"/>
     </row>
-    <row r="340" customFormat="false" ht="100" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="340" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F340" s="14"/>
       <c r="G340" s="1" t="s">
         <v>57</v>
@@ -9807,7 +10023,7 @@
       <c r="K340" s="5" t="s">
         <v>557</v>
       </c>
-      <c r="L340" s="5" t="s">
+      <c r="L340" s="2" t="s">
         <v>558</v>
       </c>
     </row>
@@ -9828,7 +10044,7 @@
       <c r="K341" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="L341" s="16" t="s">
+      <c r="L341" s="2" t="s">
         <v>562</v>
       </c>
     </row>
@@ -9861,7 +10077,7 @@
       <c r="J343" s="4"/>
       <c r="K343" s="5"/>
     </row>
-    <row r="344" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="344" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F344" s="14"/>
       <c r="G344" s="1" t="s">
         <v>57</v>
@@ -9875,7 +10091,7 @@
       <c r="K344" s="5" t="s">
         <v>568</v>
       </c>
-      <c r="L344" s="16" t="s">
+      <c r="L344" s="2" t="s">
         <v>569</v>
       </c>
     </row>
@@ -9943,7 +10159,7 @@
       <c r="K348" s="5" t="s">
         <v>578</v>
       </c>
-      <c r="L348" s="16" t="s">
+      <c r="L348" s="2" t="s">
         <v>579</v>
       </c>
     </row>
@@ -10052,7 +10268,7 @@
       <c r="K356" s="5" t="s">
         <v>587</v>
       </c>
-      <c r="L356" s="16" t="s">
+      <c r="L356" s="2" t="s">
         <v>588</v>
       </c>
     </row>
@@ -10103,7 +10319,7 @@
       <c r="K360" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="L360" s="16" t="s">
+      <c r="L360" s="2" t="s">
         <v>75</v>
       </c>
     </row>
@@ -10121,7 +10337,7 @@
       <c r="K361" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="L361" s="16" t="s">
+      <c r="L361" s="2" t="s">
         <v>75</v>
       </c>
     </row>
@@ -10177,7 +10393,7 @@
       <c r="K365" s="5" t="s">
         <v>600</v>
       </c>
-      <c r="L365" s="16" t="s">
+      <c r="L365" s="2" t="s">
         <v>601</v>
       </c>
     </row>
@@ -10290,7 +10506,7 @@
       <c r="K376" s="5" t="s">
         <v>614</v>
       </c>
-      <c r="L376" s="16" t="s">
+      <c r="L376" s="2" t="s">
         <v>615</v>
       </c>
     </row>
@@ -10338,17 +10554,17 @@
       <c r="I379" s="1" t="n">
         <v>224</v>
       </c>
-      <c r="J379" s="17" t="s">
+      <c r="J379" s="16" t="s">
         <v>622</v>
       </c>
       <c r="K379" s="5" t="s">
         <v>623</v>
       </c>
-      <c r="L379" s="18" t="s">
+      <c r="L379" s="2" t="s">
         <v>624</v>
       </c>
     </row>
-    <row r="380" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="380" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F380" s="14"/>
       <c r="G380" s="1" t="s">
         <v>181</v>
@@ -10356,7 +10572,7 @@
       <c r="I380" s="1" t="n">
         <v>225</v>
       </c>
-      <c r="J380" s="17" t="s">
+      <c r="J380" s="16" t="s">
         <v>625</v>
       </c>
       <c r="K380" s="5" t="s">
@@ -10366,7 +10582,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="381" customFormat="false" ht="88.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="381" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F381" s="14"/>
       <c r="G381" s="1" t="s">
         <v>57</v>
@@ -10380,7 +10596,7 @@
       <c r="K381" s="5" t="s">
         <v>629</v>
       </c>
-      <c r="L381" s="16" t="s">
+      <c r="L381" s="2" t="s">
         <v>630</v>
       </c>
     </row>
@@ -10484,7 +10700,7 @@
       <c r="I394" s="1" t="n">
         <v>232</v>
       </c>
-      <c r="J394" s="17" t="s">
+      <c r="J394" s="16" t="s">
         <v>641</v>
       </c>
       <c r="K394" s="5" t="s">
@@ -10494,7 +10710,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="395" customFormat="false" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="395" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F395" s="14"/>
       <c r="G395" s="1" t="s">
         <v>57</v>
@@ -10502,7 +10718,7 @@
       <c r="I395" s="1" t="n">
         <v>233</v>
       </c>
-      <c r="J395" s="17" t="s">
+      <c r="J395" s="16" t="s">
         <v>644</v>
       </c>
       <c r="K395" s="5" t="s">
@@ -10544,7 +10760,7 @@
       <c r="K397" s="5" t="s">
         <v>651</v>
       </c>
-      <c r="L397" s="19" t="s">
+      <c r="L397" s="2" t="s">
         <v>652</v>
       </c>
     </row>
@@ -10560,6 +10776,699 @@
     </row>
     <row r="400" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F400" s="14"/>
+    </row>
+    <row r="401" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A401" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="F401" s="14"/>
+    </row>
+    <row r="403" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E403" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F403" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G403" s="5"/>
+      <c r="J403" s="5"/>
+    </row>
+    <row r="404" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E404" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F404" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="405" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E405" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F405" s="10" t="s">
+        <v>654</v>
+      </c>
+      <c r="J405" s="4"/>
+      <c r="K405" s="5"/>
+    </row>
+    <row r="406" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E406" s="5"/>
+      <c r="F406" s="9"/>
+      <c r="J406" s="5"/>
+      <c r="K406" s="5"/>
+    </row>
+    <row r="407" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E407" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F407" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="J407" s="5"/>
+      <c r="K407" s="5"/>
+    </row>
+    <row r="408" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E408" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F408" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J408" s="16"/>
+      <c r="K408" s="5"/>
+    </row>
+    <row r="409" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J409" s="16"/>
+      <c r="K409" s="5"/>
+    </row>
+    <row r="410" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G410" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I410" s="1" t="n">
+        <v>250</v>
+      </c>
+      <c r="J410" s="11" t="s">
+        <v>655</v>
+      </c>
+      <c r="K410" s="5" t="s">
+        <v>656</v>
+      </c>
+      <c r="L410" s="2" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="411" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G411" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I411" s="1" t="n">
+        <v>251</v>
+      </c>
+      <c r="J411" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="K411" s="5" t="s">
+        <v>659</v>
+      </c>
+      <c r="L411" s="2" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="412" customFormat="false" ht="36.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G412" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I412" s="1" t="n">
+        <v>252</v>
+      </c>
+      <c r="J412" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="K412" s="5" t="s">
+        <v>662</v>
+      </c>
+      <c r="L412" s="2" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="413" customFormat="false" ht="49.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G413" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I413" s="1" t="n">
+        <v>253</v>
+      </c>
+      <c r="J413" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="K413" s="5" t="s">
+        <v>665</v>
+      </c>
+      <c r="L413" s="17" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="414" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G414" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I414" s="1" t="n">
+        <v>254</v>
+      </c>
+      <c r="J414" s="11" t="s">
+        <v>667</v>
+      </c>
+      <c r="K414" s="5" t="s">
+        <v>668</v>
+      </c>
+      <c r="L414" s="2" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="415" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G415" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I415" s="1" t="n">
+        <v>255</v>
+      </c>
+      <c r="J415" s="4" t="s">
+        <v>670</v>
+      </c>
+      <c r="K415" s="5" t="s">
+        <v>671</v>
+      </c>
+      <c r="L415" s="2" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="416" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G416" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I416" s="1" t="n">
+        <v>256</v>
+      </c>
+      <c r="J416" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="K416" s="5" t="s">
+        <v>674</v>
+      </c>
+      <c r="L416" s="17" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="417" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G417" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I417" s="1" t="n">
+        <v>257</v>
+      </c>
+      <c r="J417" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="K417" s="5" t="s">
+        <v>677</v>
+      </c>
+      <c r="L417" s="2" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="418" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G418" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I418" s="1" t="n">
+        <v>258</v>
+      </c>
+      <c r="J418" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="K418" s="5" t="s">
+        <v>680</v>
+      </c>
+      <c r="L418" s="2" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="419" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G419" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I419" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="J419" s="4" t="s">
+        <v>682</v>
+      </c>
+      <c r="K419" s="5" t="s">
+        <v>683</v>
+      </c>
+      <c r="L419" s="2" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="420" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G420" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I420" s="1" t="n">
+        <v>260</v>
+      </c>
+      <c r="J420" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="K420" s="5" t="s">
+        <v>686</v>
+      </c>
+      <c r="L420" s="18" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="421" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G421" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I421" s="1" t="n">
+        <v>261</v>
+      </c>
+      <c r="J421" s="4" t="s">
+        <v>688</v>
+      </c>
+      <c r="K421" s="8" t="s">
+        <v>689</v>
+      </c>
+      <c r="L421" s="2" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="422" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G422" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="I422" s="1" t="n">
+        <v>262</v>
+      </c>
+      <c r="J422" s="4" t="s">
+        <v>691</v>
+      </c>
+      <c r="K422" s="5" t="s">
+        <v>692</v>
+      </c>
+      <c r="L422" s="2" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="423" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G423" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I423" s="1" t="n">
+        <v>263</v>
+      </c>
+      <c r="J423" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="K423" s="5" t="s">
+        <v>695</v>
+      </c>
+      <c r="L423" s="18" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="424" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J424" s="4"/>
+      <c r="K424" s="5"/>
+    </row>
+    <row r="425" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E425" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F425" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J425" s="4"/>
+      <c r="K425" s="5"/>
+    </row>
+    <row r="426" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E426" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F426" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="J426" s="4"/>
+      <c r="K426" s="5"/>
+    </row>
+    <row r="427" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E427" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F427" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G427" s="5"/>
+      <c r="J427" s="4"/>
+      <c r="K427" s="5"/>
+    </row>
+    <row r="428" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J428" s="16"/>
+      <c r="K428" s="5"/>
+    </row>
+    <row r="429" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F429" s="14"/>
+      <c r="G429" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="I429" s="1" t="n">
+        <v>264</v>
+      </c>
+      <c r="J429" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="K429" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="L429" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="430" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F430" s="14"/>
+      <c r="G430" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="I430" s="1" t="n">
+        <v>265</v>
+      </c>
+      <c r="J430" s="4" t="s">
+        <v>697</v>
+      </c>
+      <c r="K430" s="5" t="s">
+        <v>698</v>
+      </c>
+      <c r="L430" s="18" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="431" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F431" s="14"/>
+      <c r="G431" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="I431" s="1" t="n">
+        <v>266</v>
+      </c>
+      <c r="J431" s="4" t="s">
+        <v>700</v>
+      </c>
+      <c r="K431" s="8" t="s">
+        <v>701</v>
+      </c>
+      <c r="L431" s="2" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="432" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F432" s="14"/>
+      <c r="G432" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="I432" s="1" t="n">
+        <v>267</v>
+      </c>
+      <c r="J432" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="K432" s="5" t="s">
+        <v>704</v>
+      </c>
+      <c r="L432" s="2" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="433" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F433" s="14"/>
+      <c r="G433" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I433" s="1" t="n">
+        <v>268</v>
+      </c>
+      <c r="J433" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="K433" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="L433" s="18" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="434" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F434" s="14"/>
+      <c r="G434" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I434" s="1" t="n">
+        <v>269</v>
+      </c>
+      <c r="J434" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="K434" s="5" t="s">
+        <v>707</v>
+      </c>
+      <c r="L434" s="2" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="435" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F435" s="14"/>
+      <c r="G435" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="I435" s="1" t="n">
+        <v>270</v>
+      </c>
+      <c r="J435" s="4" t="s">
+        <v>709</v>
+      </c>
+      <c r="K435" s="5" t="s">
+        <v>710</v>
+      </c>
+      <c r="L435" s="18" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="436" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F436" s="14"/>
+      <c r="G436" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="I436" s="1" t="n">
+        <v>271</v>
+      </c>
+      <c r="J436" s="19" t="s">
+        <v>712</v>
+      </c>
+      <c r="K436" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="L436" s="20" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="437" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F437" s="14"/>
+      <c r="G437" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I437" s="1" t="n">
+        <v>272</v>
+      </c>
+      <c r="J437" s="4" t="s">
+        <v>715</v>
+      </c>
+      <c r="K437" s="5" t="s">
+        <v>716</v>
+      </c>
+      <c r="L437" s="18" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="438" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F438" s="14"/>
+      <c r="G438" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="I438" s="1" t="n">
+        <v>273</v>
+      </c>
+      <c r="J438" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="K438" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="L438" s="18" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="439" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F439" s="14"/>
+      <c r="G439" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I439" s="1" t="n">
+        <v>274</v>
+      </c>
+      <c r="J439" s="4" t="s">
+        <v>718</v>
+      </c>
+      <c r="K439" s="5" t="s">
+        <v>719</v>
+      </c>
+      <c r="L439" s="2" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="440" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F440" s="14"/>
+      <c r="G440" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I440" s="1" t="n">
+        <v>275</v>
+      </c>
+      <c r="J440" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="K440" s="5" t="s">
+        <v>722</v>
+      </c>
+      <c r="L440" s="18" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="441" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F441" s="14"/>
+      <c r="G441" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="I441" s="1" t="n">
+        <v>276</v>
+      </c>
+      <c r="J441" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="K441" s="5" t="s">
+        <v>722</v>
+      </c>
+      <c r="L441" s="18" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="442" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F442" s="14"/>
+      <c r="G442" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="I442" s="1" t="n">
+        <v>277</v>
+      </c>
+      <c r="J442" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="K442" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="L442" s="18" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="443" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F443" s="14"/>
+      <c r="G443" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="I443" s="1" t="n">
+        <v>278</v>
+      </c>
+      <c r="J443" s="4" t="s">
+        <v>724</v>
+      </c>
+      <c r="K443" s="5" t="s">
+        <v>725</v>
+      </c>
+      <c r="L443" s="2" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="444" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F444" s="14"/>
+      <c r="G444" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="I444" s="1" t="n">
+        <v>279</v>
+      </c>
+      <c r="J444" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="K444" s="5" t="s">
+        <v>728</v>
+      </c>
+      <c r="L444" s="18" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="445" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F445" s="14"/>
+      <c r="G445" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="I445" s="1" t="n">
+        <v>280</v>
+      </c>
+      <c r="J445" s="19" t="s">
+        <v>730</v>
+      </c>
+      <c r="K445" s="5" t="s">
+        <v>731</v>
+      </c>
+      <c r="L445" s="2" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="446" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F446" s="14"/>
+      <c r="G446" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I446" s="1" t="n">
+        <v>281</v>
+      </c>
+      <c r="J446" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="K446" s="5" t="s">
+        <v>734</v>
+      </c>
+      <c r="L446" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="447" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F447" s="14"/>
+      <c r="J447" s="4"/>
+      <c r="K447" s="5"/>
+    </row>
+    <row r="448" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F448" s="14"/>
+      <c r="J448" s="4"/>
+      <c r="K448" s="5"/>
+    </row>
+    <row r="449" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E449" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F449" s="14"/>
+      <c r="J449" s="5"/>
+      <c r="K449" s="5"/>
+    </row>
+    <row r="450" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F450" s="14"/>
+      <c r="J450" s="5"/>
+    </row>
+    <row r="451" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E451" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F451" s="14"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I4:I374 I384:I1048576">
